--- a/exports/BRITANNIA_full_report.xlsx
+++ b/exports/BRITANNIA_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q55"/>
+  <dimension ref="A1:U55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>3.04</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44575.55208333334</v>
+        <v>44578.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>3698</v>
+        <v>3666.45</v>
       </c>
       <c r="I2" t="n">
         <v>3667.52154</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.46</v>
+        <v>-2.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.65</v>
+        <v>2.36</v>
       </c>
       <c r="M2" t="n">
         <v>0.22</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>3.82</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44593.38541666666</v>
+        <v>44593.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>3624</v>
+        <v>3660</v>
       </c>
       <c r="I3" t="n">
         <v>3643.851229041281</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>1.16</v>
+        <v>0.18</v>
       </c>
       <c r="L3" t="n">
         <v>1.26</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,25 +695,25 @@
         <v>6.54</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44603.55208333334</v>
+        <v>44606.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>3475</v>
+        <v>3405.4</v>
       </c>
       <c r="I4" t="n">
         <v>3423.749653558573</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>10</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.05</v>
+        <v>-6.96</v>
       </c>
       <c r="L4" t="n">
-        <v>6.59</v>
+        <v>7.16</v>
       </c>
       <c r="M4" t="n">
-        <v>0.82</v>
+        <v>1.35</v>
       </c>
       <c r="N4" t="n">
         <v>3.29</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>5.63</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44636.55208333334</v>
+        <v>44637.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>3307</v>
+        <v>3324</v>
       </c>
       <c r="I5" t="n">
         <v>3314.32247515794</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K5" t="n">
-        <v>2.89</v>
+        <v>2.39</v>
       </c>
       <c r="L5" t="n">
         <v>3.66</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>5.35</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44642.55208333334</v>
+        <v>44643.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>3165.3</v>
+        <v>3111</v>
       </c>
       <c r="I6" t="n">
         <v>3159.163471341772</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.77</v>
+        <v>-6.41</v>
       </c>
       <c r="L6" t="n">
-        <v>5.77</v>
+        <v>6.65</v>
       </c>
       <c r="M6" t="n">
         <v>0.31</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>6.96</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44652.55208333334</v>
+        <v>44655.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>3227</v>
+        <v>3263.75</v>
       </c>
       <c r="I7" t="n">
         <v>3240.063531567855</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.73</v>
+        <v>-4.91</v>
       </c>
       <c r="L7" t="n">
-        <v>4.05</v>
+        <v>5.27</v>
       </c>
       <c r="M7" t="n">
         <v>0.76</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>4.71</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44691.55208333334</v>
+        <v>44692.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>3237.05</v>
+        <v>3229.95</v>
       </c>
       <c r="I8" t="n">
         <v>3236.868521195746</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.82</v>
+        <v>-1.04</v>
       </c>
       <c r="L8" t="n">
         <v>3.49</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>7.47</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44701.38541666666</v>
+        <v>44701.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>3438</v>
+        <v>3445.05</v>
       </c>
       <c r="I9" t="n">
         <v>3441.725125541166</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K9" t="n">
-        <v>-6.44</v>
+        <v>-6.66</v>
       </c>
       <c r="L9" t="n">
-        <v>6.64</v>
+        <v>6.98</v>
       </c>
       <c r="M9" t="n">
         <v>2.03</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>5.97</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44718.55208333334</v>
+        <v>44719.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>3491.1</v>
+        <v>3392</v>
       </c>
       <c r="I10" t="n">
         <v>3464.834710601483</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>17</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>1.34</v>
+        <v>-1.54</v>
       </c>
       <c r="L10" t="n">
-        <v>0.47</v>
+        <v>1.66</v>
       </c>
       <c r="M10" t="n">
-        <v>0.46</v>
+        <v>0.75</v>
       </c>
       <c r="N10" t="n">
-        <v>2.89</v>
+        <v>3.14</v>
       </c>
       <c r="O10" t="n">
         <v>3.27</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>6.89</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44742.55208333334</v>
+        <v>44743.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>3441</v>
+        <v>3522</v>
       </c>
       <c r="I11" t="n">
         <v>3507.895342294774</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.44</v>
+        <v>-3.83</v>
       </c>
       <c r="L11" t="n">
-        <v>3.36</v>
+        <v>3.92</v>
       </c>
       <c r="M11" t="n">
         <v>0.77</v>
       </c>
       <c r="N11" t="n">
-        <v>1.72</v>
+        <v>3.87</v>
       </c>
       <c r="O11" t="n">
         <v>-3.14</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>7.06</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44777.55208333334</v>
+        <v>44778.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>3760</v>
+        <v>3728.6</v>
       </c>
       <c r="I12" t="n">
         <v>3751.762317997297</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K12" t="n">
-        <v>6.76</v>
+        <v>5.87</v>
       </c>
       <c r="L12" t="n">
         <v>3.12</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>6.16</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44817.38541666666</v>
+        <v>44817.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>3723.9</v>
+        <v>3751</v>
       </c>
       <c r="I13" t="n">
         <v>3745.20845801894</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>39</v>
+        <v>39.16666666666666</v>
       </c>
       <c r="K13" t="n">
-        <v>0.13</v>
+        <v>-0.6</v>
       </c>
       <c r="L13" t="n">
         <v>2.76</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>3.86</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44820.55208333334</v>
+        <v>44823.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>3630</v>
+        <v>3571.1</v>
       </c>
       <c r="I14" t="n">
         <v>3619.473536982418</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>3</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.23</v>
+        <v>-4.8</v>
       </c>
       <c r="L14" t="n">
-        <v>3.46</v>
+        <v>4.85</v>
       </c>
       <c r="M14" t="n">
         <v>1.15</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>5.19</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44824.55208333334</v>
+        <v>44825.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>3648</v>
+        <v>3758.25</v>
       </c>
       <c r="I15" t="n">
         <v>3729.204304657526</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.15</v>
+        <v>-5.24</v>
       </c>
       <c r="L15" t="n">
-        <v>2.63</v>
+        <v>6.1</v>
       </c>
       <c r="M15" t="n">
         <v>0.47</v>
       </c>
       <c r="N15" t="n">
-        <v>1.52</v>
+        <v>2.99</v>
       </c>
       <c r="O15" t="n">
         <v>-1.01</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>5.98</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44858.76041666666</v>
+        <v>44859.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>3794</v>
+        <v>3700</v>
       </c>
       <c r="I16" t="n">
         <v>3716.610634205545</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>33.375</v>
+        <v>34</v>
       </c>
       <c r="K16" t="n">
-        <v>0.95</v>
+        <v>-1.55</v>
       </c>
       <c r="L16" t="n">
         <v>3.23</v>
@@ -1353,7 +1544,7 @@
         <v>0.85</v>
       </c>
       <c r="N16" t="n">
-        <v>2.32</v>
+        <v>2.61</v>
       </c>
       <c r="O16" t="n">
         <v>2.99</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>5.44</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44869.55208333334</v>
+        <v>44872.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>3796.85</v>
+        <v>4149.55</v>
       </c>
       <c r="I17" t="n">
         <v>3853.224225226279</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.62</v>
+        <v>-12.15</v>
       </c>
       <c r="L17" t="n">
-        <v>3.1</v>
+        <v>13.24</v>
       </c>
       <c r="M17" t="n">
-        <v>0.96</v>
+        <v>3.51</v>
       </c>
       <c r="N17" t="n">
-        <v>1.23</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="O17" t="n">
         <v>-2.61</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>8.07</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44917.55208333334</v>
+        <v>44918.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>4390</v>
+        <v>4333.45</v>
       </c>
       <c r="I18" t="n">
         <v>4373.622663647218</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K18" t="n">
-        <v>5.79</v>
+        <v>4.43</v>
       </c>
       <c r="L18" t="n">
         <v>5.29</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>4.25</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44950.38541666666</v>
+        <v>44950.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>4374.5</v>
+        <v>4405.05</v>
       </c>
       <c r="I19" t="n">
         <v>4399.001073664578</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>32</v>
+        <v>32.16666666666666</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.95</v>
+        <v>-1.65</v>
       </c>
       <c r="L19" t="n">
         <v>2.04</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>3.43</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44977.38541666666</v>
+        <v>44977.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>4472.8</v>
+        <v>4447</v>
       </c>
       <c r="I20" t="n">
         <v>4468.989082418054</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>26.83333333333333</v>
+        <v>27</v>
       </c>
       <c r="K20" t="n">
-        <v>1.54</v>
+        <v>0.95</v>
       </c>
       <c r="L20" t="n">
         <v>1.93</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>3.54</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45033.38541666666</v>
+        <v>45033.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>4334.6</v>
+        <v>4348.75</v>
       </c>
       <c r="I21" t="n">
         <v>4337.762298348644</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>55.83333333333334</v>
+        <v>56</v>
       </c>
       <c r="K21" t="n">
-        <v>2.53</v>
+        <v>2.21</v>
       </c>
       <c r="L21" t="n">
         <v>2.09</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>4.07</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45064.55208333334</v>
+        <v>45065.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>4569</v>
+        <v>4497</v>
       </c>
       <c r="I22" t="n">
         <v>4507.026774004534</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>31</v>
+        <v>31.83333333333333</v>
       </c>
       <c r="K22" t="n">
-        <v>5.06</v>
+        <v>3.41</v>
       </c>
       <c r="L22" t="n">
         <v>2.36</v>
@@ -1695,7 +1958,7 @@
         <v>0.44</v>
       </c>
       <c r="N22" t="n">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="O22" t="n">
         <v>2.2</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>4.82</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45078.55208333334</v>
+        <v>45079.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>4625</v>
+        <v>4657.1</v>
       </c>
       <c r="I23" t="n">
         <v>4643.341121424425</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.85</v>
+        <v>-3.56</v>
       </c>
       <c r="L23" t="n">
-        <v>4.63</v>
+        <v>4.93</v>
       </c>
       <c r="M23" t="n">
         <v>1.44</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>3.38</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45128.55208333334</v>
+        <v>45131.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>5022</v>
+        <v>4984.95</v>
       </c>
       <c r="I24" t="n">
         <v>5003.094547181568</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>52</v>
       </c>
       <c r="K24" t="n">
-        <v>7.84</v>
+        <v>7.04</v>
       </c>
       <c r="L24" t="n">
         <v>0.47</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>4.29</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45181.55208333334</v>
+        <v>45182.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>4571.9</v>
+        <v>4600.25</v>
       </c>
       <c r="I25" t="n">
         <v>4587.566710594433</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>50.16666666666666</v>
+        <v>51</v>
       </c>
       <c r="K25" t="n">
-        <v>8.289999999999999</v>
+        <v>7.72</v>
       </c>
       <c r="L25" t="n">
         <v>1.26</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>3</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45226.55208333334</v>
+        <v>45229.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>4520</v>
+        <v>4492.25</v>
       </c>
       <c r="I26" t="n">
         <v>4496.455835782862</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.74</v>
+        <v>-2.35</v>
       </c>
       <c r="L26" t="n">
-        <v>2.9</v>
+        <v>3.46</v>
       </c>
       <c r="M26" t="n">
         <v>1.13</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>3.1</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45233.55208333334</v>
+        <v>45236.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>4545</v>
+        <v>4604.9</v>
       </c>
       <c r="I27" t="n">
         <v>4566.25353374351</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.17</v>
+        <v>-2.51</v>
       </c>
       <c r="L27" t="n">
-        <v>2.01</v>
+        <v>2.64</v>
       </c>
       <c r="M27" t="n">
         <v>2.88</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>4.72</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45275.55208333334</v>
+        <v>45278.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>4929.15</v>
+        <v>4850.65</v>
       </c>
       <c r="I28" t="n">
         <v>4870.037006817324</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K28" t="n">
-        <v>7.04</v>
+        <v>5.34</v>
       </c>
       <c r="L28" t="n">
         <v>1.28</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>4.31</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45280.55208333334</v>
+        <v>45281.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>4925</v>
+        <v>5050</v>
       </c>
       <c r="I29" t="n">
         <v>5036.360401559865</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.53</v>
+        <v>-4.11</v>
       </c>
       <c r="L29" t="n">
-        <v>4.15</v>
+        <v>5.41</v>
       </c>
       <c r="M29" t="n">
         <v>0.2</v>
       </c>
       <c r="N29" t="n">
-        <v>0.45</v>
+        <v>2.84</v>
       </c>
       <c r="O29" t="n">
         <v>-0.83</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>6.02</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45300.55208333334</v>
+        <v>45301.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>5114</v>
+        <v>5060.25</v>
       </c>
       <c r="I30" t="n">
         <v>5113.323743260194</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K30" t="n">
-        <v>1.27</v>
+        <v>0.2</v>
       </c>
       <c r="L30" t="n">
         <v>3.41</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>5.11</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45407.38541666666</v>
+        <v>45407.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>4808</v>
+        <v>4847.3</v>
       </c>
       <c r="I31" t="n">
         <v>4842.639714184453</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>106</v>
+        <v>106.1666666666667</v>
       </c>
       <c r="K31" t="n">
-        <v>4.98</v>
+        <v>4.21</v>
       </c>
       <c r="L31" t="n">
         <v>3.76</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>140</v>
+        <v>141</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>3.59</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45505.38541666666</v>
+        <v>45505.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>5754</v>
+        <v>5700</v>
       </c>
       <c r="I32" t="n">
         <v>5706.330292797595</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>97.83333333333333</v>
+        <v>98</v>
       </c>
       <c r="K32" t="n">
-        <v>18.71</v>
+        <v>17.59</v>
       </c>
       <c r="L32" t="n">
         <v>2.88</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>133</v>
+        <v>134</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>4.52</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45534.55208333334</v>
+        <v>45537.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>5866</v>
+        <v>5891.45</v>
       </c>
       <c r="I33" t="n">
         <v>5888.377181449744</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>29</v>
+        <v>31.83333333333333</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.91</v>
+        <v>-3.36</v>
       </c>
       <c r="L33" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="M33" t="n">
         <v>0.86</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>3.47</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45569.55208333334</v>
+        <v>45572.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>6200</v>
+        <v>6120</v>
       </c>
       <c r="I34" t="n">
         <v>6189.511574494551</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K34" t="n">
-        <v>5.24</v>
+        <v>3.88</v>
       </c>
       <c r="L34" t="n">
         <v>1.09</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>5.43</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45665.55208333334</v>
+        <v>45666.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>4856</v>
+        <v>4953.6</v>
       </c>
       <c r="I35" t="n">
         <v>4865.846059672067</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>93.16666666666667</v>
+        <v>94</v>
       </c>
       <c r="K35" t="n">
-        <v>20.65</v>
+        <v>19.06</v>
       </c>
       <c r="L35" t="n">
         <v>1.88</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>129</v>
+        <v>130</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>4.73</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45693.38541666666</v>
+        <v>45693.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>4976.3</v>
+        <v>4930</v>
       </c>
       <c r="I36" t="n">
         <v>4950.626374001269</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K36" t="n">
-        <v>0.46</v>
+        <v>-0.48</v>
       </c>
       <c r="L36" t="n">
         <v>4.25</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>6.89</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45723.55208333334</v>
+        <v>45726.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>4752.7</v>
+        <v>4791</v>
       </c>
       <c r="I37" t="n">
         <v>4776.3123197455</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>30</v>
+        <v>32.83333333333334</v>
       </c>
       <c r="K37" t="n">
-        <v>3.6</v>
+        <v>2.82</v>
       </c>
       <c r="L37" t="n">
         <v>2.95</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>5.6</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45861.55208333334</v>
+        <v>45862.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>5733</v>
+        <v>5671.5</v>
       </c>
       <c r="I38" t="n">
         <v>5679.82411753547</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>135.1666666666667</v>
+        <v>136</v>
       </c>
       <c r="K38" t="n">
-        <v>19.66</v>
+        <v>18.38</v>
       </c>
       <c r="L38" t="n">
         <v>3.99</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>182</v>
+        <v>183</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>5</v>
+      </c>
+      <c r="U38" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -2643,25 +3110,25 @@
         <v>4.18</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45869.55208333334</v>
+        <v>45870.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>5765</v>
+        <v>5833.5</v>
       </c>
       <c r="I39" t="n">
         <v>5795.86370542454</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.65</v>
+        <v>-2.86</v>
       </c>
       <c r="L39" t="n">
-        <v>2.71</v>
+        <v>4.01</v>
       </c>
       <c r="M39" t="n">
-        <v>0.37</v>
+        <v>0.6</v>
       </c>
       <c r="N39" t="n">
         <v>1.44</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>3.94</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45874.55208333334</v>
+        <v>45875.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>5640</v>
+        <v>5411.5</v>
       </c>
       <c r="I40" t="n">
         <v>5603.572612361573</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K40" t="n">
-        <v>-3.32</v>
+        <v>-7.23</v>
       </c>
       <c r="L40" t="n">
-        <v>3.82</v>
+        <v>7.93</v>
       </c>
       <c r="M40" t="n">
         <v>1</v>
       </c>
       <c r="N40" t="n">
-        <v>2.19</v>
+        <v>4.43</v>
       </c>
       <c r="O40" t="n">
         <v>0.79</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>7.19</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45888.55208333334</v>
+        <v>45889.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>5510</v>
+        <v>5640</v>
       </c>
       <c r="I41" t="n">
         <v>5533.896449563085</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K41" t="n">
-        <v>-1.82</v>
+        <v>-4.22</v>
       </c>
       <c r="L41" t="n">
         <v>4.72</v>
@@ -2778,7 +3269,7 @@
         <v>1.75</v>
       </c>
       <c r="N41" t="n">
-        <v>2.32</v>
+        <v>3.63</v>
       </c>
       <c r="O41" t="n">
         <v>-4.43</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>6.8</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45922.55208333334</v>
+        <v>45923.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>6054.5</v>
+        <v>5980.5</v>
       </c>
       <c r="I42" t="n">
         <v>6019.943448355717</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K42" t="n">
-        <v>7.35</v>
+        <v>6.04</v>
       </c>
       <c r="L42" t="n">
         <v>2.92</v>
@@ -2835,7 +3338,7 @@
         <v>0.87</v>
       </c>
       <c r="N42" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="O42" t="n">
         <v>3.63</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>4.12</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45946.38541666666</v>
+        <v>45946.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>5970</v>
+        <v>6030</v>
       </c>
       <c r="I43" t="n">
         <v>5992.807731257417</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K43" t="n">
-        <v>0.18</v>
+        <v>-0.83</v>
       </c>
       <c r="L43" t="n">
         <v>1.49</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>3.99</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45957.55208333334</v>
+        <v>45958.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>5926</v>
+        <v>5824</v>
       </c>
       <c r="I44" t="n">
         <v>5889.904480085069</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.72</v>
+        <v>-3.42</v>
       </c>
       <c r="L44" t="n">
         <v>3.62</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>5.39</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45967.55208333334</v>
+        <v>45968.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>6016</v>
+        <v>6137.5</v>
       </c>
       <c r="I45" t="n">
         <v>6047.120608666886</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K45" t="n">
-        <v>-3.3</v>
+        <v>-5.38</v>
       </c>
       <c r="L45" t="n">
         <v>6.31</v>
@@ -3006,7 +3545,7 @@
         <v>4.63</v>
       </c>
       <c r="N45" t="n">
-        <v>1.76</v>
+        <v>2.39</v>
       </c>
       <c r="O45" t="n">
         <v>-0.6899999999999999</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>6.72</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45971.55208333334</v>
+        <v>45972.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>6135</v>
+        <v>5895.5</v>
       </c>
       <c r="I46" t="n">
         <v>5921.972590916042</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.04</v>
+        <v>-3.94</v>
       </c>
       <c r="L46" t="n">
-        <v>3.65</v>
+        <v>6.75</v>
       </c>
       <c r="M46" t="n">
-        <v>0.76</v>
+        <v>3.02</v>
       </c>
       <c r="N46" t="n">
-        <v>0.41</v>
+        <v>2.93</v>
       </c>
       <c r="O46" t="n">
         <v>2.39</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>5.42</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46003.55208333334</v>
+        <v>46006.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>5905</v>
+        <v>6032</v>
       </c>
       <c r="I47" t="n">
         <v>5969.643231554928</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.16</v>
+        <v>-2.32</v>
       </c>
       <c r="L47" t="n">
-        <v>1.52</v>
+        <v>2.55</v>
       </c>
       <c r="M47" t="n">
         <v>0.38</v>
       </c>
       <c r="N47" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="O47" t="n">
         <v>-2.93</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>5.17</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46030.55208333334</v>
+        <v>46031.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>6022</v>
+        <v>5964.5</v>
       </c>
       <c r="I48" t="n">
         <v>5985.651084439248</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.17</v>
+        <v>-1.12</v>
       </c>
       <c r="L48" t="n">
         <v>2.9</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,25 +3800,25 @@
         <v>5.85</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46063.55208333334</v>
+        <v>46064.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>5875</v>
+        <v>6065</v>
       </c>
       <c r="I49" t="n">
         <v>5965.300191420466</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K49" t="n">
-        <v>1.5</v>
+        <v>-1.68</v>
       </c>
       <c r="L49" t="n">
-        <v>2.38</v>
+        <v>3.21</v>
       </c>
       <c r="M49" t="n">
-        <v>0.86</v>
+        <v>2.13</v>
       </c>
       <c r="N49" t="n">
         <v>3.29</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,25 +3869,25 @@
         <v>4.77</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>6000</v>
+        <v>5954</v>
       </c>
       <c r="I50" t="n">
         <v>5957.84294469628</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K50" t="n">
-        <v>-1.07</v>
+        <v>-1.83</v>
       </c>
       <c r="L50" t="n">
-        <v>1.66</v>
+        <v>3.28</v>
       </c>
       <c r="M50" t="n">
-        <v>0.38</v>
+        <v>2.23</v>
       </c>
       <c r="N50" t="n">
         <v>2.12</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>3.91</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46129.38541666666</v>
+        <v>46129.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>5720</v>
+        <v>5740</v>
       </c>
       <c r="I51" t="n">
         <v>5733.169796386108</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>46</v>
+        <v>46.16666666666666</v>
       </c>
       <c r="K51" t="n">
-        <v>3.93</v>
+        <v>3.59</v>
       </c>
       <c r="L51" t="n">
         <v>0.99</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>5.63</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46149.55208333334</v>
+        <v>46150.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>5885.5</v>
+        <v>5524.5</v>
       </c>
       <c r="I52" t="n">
         <v>5593.569895820776</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K52" t="n">
-        <v>2.53</v>
+        <v>-3.75</v>
       </c>
       <c r="L52" t="n">
-        <v>1.73</v>
+        <v>4.13</v>
       </c>
       <c r="M52" t="n">
-        <v>0.43</v>
+        <v>4.27</v>
       </c>
       <c r="N52" t="n">
-        <v>2.22</v>
+        <v>6.28</v>
       </c>
       <c r="O52" t="n">
         <v>2.5</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>7.15</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46196.55208333334</v>
+        <v>46197.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>5230.5</v>
+        <v>5262.5</v>
       </c>
       <c r="I53" t="n">
         <v>5251.059061705922</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K53" t="n">
-        <v>5.32</v>
+        <v>4.74</v>
       </c>
       <c r="L53" t="n">
         <v>2.34</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>3.09</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46254.55208333334</v>
+        <v>46255.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>5536</v>
+        <v>5359</v>
       </c>
       <c r="I54" t="n">
         <v>5421.09842162777</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>57.16666666666666</v>
+        <v>58</v>
       </c>
       <c r="K54" t="n">
-        <v>5.2</v>
+        <v>1.83</v>
       </c>
       <c r="L54" t="n">
         <v>3.55</v>
@@ -3519,7 +4166,7 @@
         <v>1.77</v>
       </c>
       <c r="N54" t="n">
-        <v>2.26</v>
+        <v>3.09</v>
       </c>
       <c r="O54" t="n">
         <v>0.77</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3579,6 +4238,14 @@
       <c r="Q55" t="n">
         <v>90</v>
       </c>
+      <c r="R55" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5681,7 +6348,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.6</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="6">
@@ -5691,7 +6358,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="7">
@@ -5701,7 +6368,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>135.2</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8">
@@ -5711,7 +6378,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -5721,7 +6388,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="10">
@@ -5731,7 +6398,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>54.7</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="11">
@@ -5741,7 +6408,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
@@ -5751,7 +6418,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13">
@@ -5761,7 +6428,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>54.7</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="14">
@@ -5771,7 +6438,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.81</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="15">
@@ -5781,7 +6448,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.72</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="16">
@@ -5791,7 +6458,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.86</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="17">
@@ -5801,7 +6468,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20.65</v>
+        <v>19.06</v>
       </c>
     </row>
     <row r="18">
@@ -5811,7 +6478,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52.8</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="19">
@@ -5821,7 +6488,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.02</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="20">
@@ -5831,7 +6498,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.92</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="21">
@@ -5841,7 +6508,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6.64</v>
+        <v>13.24</v>
       </c>
     </row>
     <row r="22">
@@ -5851,7 +6518,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
@@ -5861,7 +6528,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -5871,7 +6538,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="25">
@@ -5891,7 +6558,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.18</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="27">
@@ -5901,7 +6568,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.42</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -5911,7 +6578,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
